--- a/appointment_forms/017_performance_evaluation_slot_booking_form--appointment_forms.xlsx
+++ b/appointment_forms/017_performance_evaluation_slot_booking_form--appointment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,7 +515,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -525,13 +525,13 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Performance Evaluation</t>
+          <t>Performance Status</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>form_page_2</t>
+          <t>slot_booking_details</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Slot Booking</t>
+          <t>Slot Booking Details</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -600,7 +600,7 @@
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -617,7 +617,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Reviewers</t>
+          <t>Form Page 5</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>form_page_6</t>
+          <t>reviewer_info</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Reviewers</t>
+          <t>Reviewer Information</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -663,13 +663,13 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Reviewers</t>
+          <t>Reviewer Email</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -686,13 +686,105 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Reviewers</t>
+          <t>Reviewer Contact Method</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>form_page_9</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Additional Comments</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>form_page_10</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Slot Duration</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>form_page_11</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Start Time</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>form_page_12</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>End Time</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -711,7 +803,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
@@ -740,12 +832,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -757,12 +849,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -774,12 +866,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -791,12 +883,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -808,12 +900,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -825,12 +917,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
